--- a/sample_data/sample_output/OP0322F_customized.xlsx
+++ b/sample_data/sample_output/OP0322F_customized.xlsx
@@ -18,9 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="165" formatCode="$#,##0.00"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="166" formatCode="$#,##0.00"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -60,11 +61,11 @@
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -483,7 +484,7 @@
   <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -554,10 +555,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A2" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -597,10 +596,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A3" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -640,10 +637,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A4" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -683,10 +678,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A5" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -726,10 +719,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A6" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -769,10 +760,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A7" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -812,10 +801,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A8" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -855,10 +842,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A9" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -898,10 +883,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A10" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -941,10 +924,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A11" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -984,10 +965,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A12" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -1027,10 +1006,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A13" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -1070,10 +1047,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A14" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -1113,10 +1088,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A15" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -1156,10 +1129,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A16" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -1199,10 +1170,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A17" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -1244,10 +1213,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A18" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -1289,10 +1256,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A19" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -1334,10 +1299,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A20" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -1379,10 +1342,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A21" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -1424,10 +1385,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A22" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
@@ -1469,10 +1428,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A23" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -1514,10 +1471,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A24" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -1559,10 +1514,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A25" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -1604,10 +1557,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A26" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
@@ -1649,10 +1600,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A27" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -1694,10 +1643,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A28" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -1739,10 +1686,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A29" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -1784,10 +1729,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A30" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -1829,10 +1772,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A31" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
@@ -1874,10 +1815,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A32" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -1919,10 +1858,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A33" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
@@ -1964,10 +1901,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A34" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
@@ -2009,10 +1944,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A35" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
@@ -2054,10 +1987,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A36" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
@@ -2099,10 +2030,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A37" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -2144,10 +2073,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A38" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
@@ -2189,10 +2116,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A39" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
@@ -2234,10 +2159,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A40" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
@@ -2279,10 +2202,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A41" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
@@ -2324,10 +2245,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A42" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
@@ -2369,10 +2288,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A43" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
@@ -2414,10 +2331,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A44" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
@@ -2459,10 +2374,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A45" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
@@ -2504,10 +2417,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A46" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
@@ -2549,10 +2460,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A47" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
@@ -2594,10 +2503,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A48" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
@@ -2639,10 +2546,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A49" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
@@ -2684,10 +2589,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A50" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
@@ -2729,10 +2632,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A51" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
@@ -2774,10 +2675,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A52" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
@@ -2819,10 +2718,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A53" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
@@ -2864,10 +2761,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A54" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
@@ -2909,10 +2804,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A55" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
@@ -2954,10 +2847,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A56" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
@@ -2999,10 +2890,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A57" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
@@ -3044,10 +2933,8 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A58" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
@@ -3089,10 +2976,8 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A59" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
@@ -3134,10 +3019,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A60" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
@@ -3179,10 +3062,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A61" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
@@ -3224,10 +3105,8 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A62" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
@@ -3269,10 +3148,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A63" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
@@ -3314,10 +3191,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A64" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
@@ -3359,10 +3234,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A65" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
@@ -3404,10 +3277,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A66" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
@@ -3449,10 +3320,8 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A67" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
@@ -3494,10 +3363,8 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A68" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
@@ -3539,10 +3406,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A69" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
@@ -3584,10 +3449,8 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A70" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
@@ -3629,10 +3492,8 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>03/22/2026</t>
-        </is>
+      <c r="A71" s="2" t="n">
+        <v>46103</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
